--- a/Pruebas calificadas/COLEGIO MARIA-CURREA-MANRIQUE-(IED)-1101_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO MARIA-CURREA-MANRIQUE-(IED)-1101_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -2325,11 +2301,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -2578,11 +2550,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -2831,11 +2799,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -3084,11 +3048,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -3337,11 +3297,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -3590,11 +3546,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -3602,7 +3554,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MARIA CURREA MANRIQUE (IED)</t>
+          <t>MARIA CURREA MANRIQUE (IED)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3843,11 +3795,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -4096,11 +4044,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -4108,7 +4052,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MARIA CURREA MANRIQUE (IED)</t>
+          <t>MARIA CURREA MANRIQUE (IED)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4349,11 +4293,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -4602,11 +4542,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -4614,7 +4550,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MARIA CURREA MANRIQUE (IED)</t>
+          <t>MARIA CURREA MANRIQUE (IED)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4855,11 +4791,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -5028,11 +4960,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -5281,11 +5209,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -5534,11 +5458,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -5787,11 +5707,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -6040,11 +5956,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -6293,11 +6205,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -6546,11 +6454,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -6799,11 +6703,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -7048,11 +6948,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -7301,11 +7197,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -7313,7 +7205,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MARIA CURREA MANRIQUE (IED)</t>
+          <t>MARIA CURREA MANRIQUE (IED)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7554,11 +7446,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -7807,11 +7695,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -8060,11 +7944,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -8233,11 +8113,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -8486,11 +8362,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -8739,11 +8611,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -8992,11 +8860,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -9245,11 +9109,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -9498,11 +9358,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -9751,11 +9607,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -9763,7 +9615,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MARIA CURREA MANRIQUE (IED)</t>
+          <t>MARIA CURREA MANRIQUE (IED)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -9924,11 +9776,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -10177,11 +10025,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -10430,11 +10274,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -10683,11 +10523,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -10936,11 +10772,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -10948,7 +10780,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MARIA CURREA MANRIQUE (IED)</t>
+          <t>MARIA CURREA MANRIQUE (IED)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11189,11 +11021,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -11442,11 +11270,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -11695,11 +11519,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -11948,11 +11768,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -12197,11 +12013,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -12450,11 +12262,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -12703,11 +12511,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -12956,11 +12760,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -12968,7 +12768,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MARIA CURREA MANRIQUE (IED)</t>
+          <t>MARIA CURREA MANRIQUE (IED)</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13209,11 +13009,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -13462,11 +13258,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -13715,11 +13507,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -13968,11 +13756,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -14221,11 +14005,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -14474,11 +14254,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -14723,11 +14499,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -14976,11 +14748,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -15229,11 +14997,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -15478,11 +15242,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -15731,11 +15491,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -15984,11 +15740,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -16237,11 +15989,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -16249,7 +15997,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MARIA CURREA MANRIQUE (IED)</t>
+          <t>MARIA CURREA MANRIQUE (IED)</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16490,11 +16238,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -16743,11 +16487,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -16996,11 +16736,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -17249,11 +16985,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -17502,11 +17234,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -17755,11 +17483,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -18004,11 +17728,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -18257,11 +17977,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -18510,11 +18226,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -18763,11 +18475,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -19016,11 +18724,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -19269,11 +18973,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -19522,11 +19222,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -19771,11 +19467,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="inlineStr"/>
       <c r="B78" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -20024,11 +19716,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A79" s="2" t="inlineStr"/>
       <c r="B79" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -20273,11 +19961,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A80" s="2" t="inlineStr"/>
       <c r="B80" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -20526,11 +20210,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A81" s="2" t="inlineStr"/>
       <c r="B81" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -20779,11 +20459,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A82" s="2" t="inlineStr"/>
       <c r="B82" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -21032,11 +20708,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A83" s="2" t="inlineStr"/>
       <c r="B83" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -21285,11 +20957,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A84" s="2" t="inlineStr"/>
       <c r="B84" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -21538,11 +21206,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A85" s="2" t="inlineStr"/>
       <c r="B85" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -21791,11 +21455,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A86" s="2" t="inlineStr"/>
       <c r="B86" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -22044,11 +21704,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A87" s="2" t="inlineStr"/>
       <c r="B87" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -22297,11 +21953,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A88" s="2" t="inlineStr"/>
       <c r="B88" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -22550,11 +22202,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A89" s="2" t="inlineStr"/>
       <c r="B89" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -22803,11 +22451,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A90" s="2" t="inlineStr"/>
       <c r="B90" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -23056,11 +22700,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A91" s="2" t="inlineStr"/>
       <c r="B91" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -23309,11 +22949,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A92" s="2" t="inlineStr"/>
       <c r="B92" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -23562,11 +23198,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A93" s="2" t="inlineStr"/>
       <c r="B93" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -23574,7 +23206,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MARIA CURREA MANRIQUE (IED)</t>
+          <t>MARIA CURREA MANRIQUE (IED)</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -23815,11 +23447,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A94" s="2" t="inlineStr"/>
       <c r="B94" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -24068,11 +23696,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A95" s="2" t="inlineStr"/>
       <c r="B95" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -24321,11 +23945,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A96" s="2" t="inlineStr"/>
       <c r="B96" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -24574,11 +24194,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A97" s="2" t="inlineStr"/>
       <c r="B97" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -24827,11 +24443,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A98" s="2" t="inlineStr"/>
       <c r="B98" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -25080,11 +24692,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A99" s="2" t="inlineStr"/>
       <c r="B99" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -25333,11 +24941,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A100" s="2" t="inlineStr"/>
       <c r="B100" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -25586,11 +25190,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A101" s="2" t="inlineStr"/>
       <c r="B101" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -25839,11 +25439,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A102" s="2" t="inlineStr"/>
       <c r="B102" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -26092,11 +25688,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A103" s="2" t="inlineStr"/>
       <c r="B103" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -26345,11 +25937,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A104" s="2" t="inlineStr"/>
       <c r="B104" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -26598,11 +26186,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A105" s="2" t="inlineStr"/>
       <c r="B105" s="2" t="inlineStr">
         <is>
           <t>111001801276</t>
@@ -26610,7 +26194,7 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO MARIA CURREA MANRIQUE (IED)</t>
+          <t>MARIA CURREA MANRIQUE (IED)</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
